--- a/HotGuy/Assets/Config/Excel/__tables__.xlsx
+++ b/HotGuy/Assets/Config/Excel/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GP\GP-TestRepo\HotGuy\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D87816-2D02-430A-9456-D69669F32A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA77DC97-E5BE-4817-A9EE-785ED34C4474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1073" yWindow="1073" windowWidth="14400" windowHeight="9840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -159,6 +159,26 @@
   </si>
   <si>
     <t>full_name</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCTaskQuoteConfigCategory</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCTaskQuoteConfig</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	SCTaskQuoteConfig.xlsx</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>list</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	SCTaskQuoteConfigCategory</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -527,23 +547,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="41.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="32.08203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="41.46484375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="32.06640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="56.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="49.58203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="49.59765625" style="2" customWidth="1"/>
     <col min="6" max="7" width="18" style="2" customWidth="1"/>
     <col min="8" max="8" width="16.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="40.83203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="40.796875" style="2" customWidth="1"/>
     <col min="10" max="10" width="9" style="2"/>
-    <col min="11" max="11" width="49.58203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="49.59765625" style="2" customWidth="1"/>
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -578,7 +598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -611,7 +631,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -638,7 +658,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.4">
       <c r="B4" s="4" t="s">
         <v>26</v>
       </c>
@@ -660,7 +680,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="15" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
         <v>29</v>
       </c>
@@ -684,7 +704,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="15" x14ac:dyDescent="0.4">
       <c r="B6" s="4" t="s">
         <v>36</v>
       </c>
@@ -706,7 +726,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="15" x14ac:dyDescent="0.4">
       <c r="B7" s="4" t="s">
         <v>37</v>
       </c>
@@ -724,6 +744,30 @@
       </c>
       <c r="K7" s="4" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15" x14ac:dyDescent="0.4">
+      <c r="B8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/HotGuy/Assets/Config/Excel/__tables__.xlsx
+++ b/HotGuy/Assets/Config/Excel/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GP\GP-TestRepo\HotGuy\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA77DC97-E5BE-4817-A9EE-785ED34C4474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3CD006-9302-472D-9571-FF0E6FEBBAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1073" yWindow="1073" windowWidth="14400" windowHeight="9840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1620" yWindow="1611" windowWidth="14374" windowHeight="9832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -180,6 +180,30 @@
   <si>
     <t xml:space="preserve">	SCTaskQuoteConfigCategory</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DanmakuPoolConfigCategory</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DanmakuPoolConfig</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DanmakuPoolConfig.xlsx</t>
+  </si>
+  <si>
+    <t>map</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DanmakuContentConfigCategory</t>
+  </si>
+  <si>
+    <t>DanmakuContentConfig</t>
+  </si>
+  <si>
+    <t>DanmakuContentConfig.xlsx</t>
   </si>
 </sst>
 </file>
@@ -547,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -770,6 +794,66 @@
         <v>45</v>
       </c>
     </row>
+    <row r="9" spans="1:11" ht="15" x14ac:dyDescent="0.4">
+      <c r="B9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15" x14ac:dyDescent="0.4">
+      <c r="B10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15" x14ac:dyDescent="0.4">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
